--- a/Exc2/FURPS_table.xlsx
+++ b/Exc2/FURPS_table.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
   <si>
     <t>Код</t>
   </si>
@@ -152,6 +152,24 @@
   </si>
   <si>
     <t>Я, как посетитель Сайта, хочу иметь возможность подать заявку на депозит с указанием своих контактных данных, для экономии времени, затрачиваемого на открытие депозита</t>
+  </si>
+  <si>
+    <t>Не дорабатывать функционал подрядчика в интернет-банке</t>
+  </si>
+  <si>
+    <t>Использовать платформы Java, .NET, PHP</t>
+  </si>
+  <si>
+    <t>Нужно использовать микросервисную архитектуру при разработке в интернет-банке</t>
+  </si>
+  <si>
+    <t>АБС поддерживает только вертикальное масштабирование</t>
+  </si>
+  <si>
+    <t>Следует избегать прямого обмена данными между онлайн-банком и АБС</t>
+  </si>
+  <si>
+    <t>Использовать существующие базы данных Oracle, MS SQL</t>
   </si>
 </sst>
 </file>
@@ -732,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr defaultColWidth="10.44140625" defaultRowHeight="13.2"/>
   <cols>
     <col min="2" max="2" width="6.88671875" customWidth="1"/>
@@ -1055,6 +1073,66 @@
       </c>
       <c r="D35" s="5"/>
     </row>
+    <row r="36" spans="1:4" ht="33" customHeight="1">
+      <c r="A36" s="7"/>
+      <c r="B36" s="6">
+        <v>4</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" s="5"/>
+    </row>
+    <row r="37" spans="1:4" ht="33" customHeight="1">
+      <c r="A37" s="7"/>
+      <c r="B37" s="6">
+        <v>5</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" s="5"/>
+    </row>
+    <row r="38" spans="1:4" ht="33" customHeight="1">
+      <c r="A38" s="7"/>
+      <c r="B38" s="6">
+        <v>6</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="D38" s="5"/>
+    </row>
+    <row r="39" spans="1:4" ht="33" customHeight="1">
+      <c r="A39" s="7"/>
+      <c r="B39" s="6">
+        <v>7</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D39" s="5"/>
+    </row>
+    <row r="40" spans="1:4" ht="33" customHeight="1">
+      <c r="A40" s="7"/>
+      <c r="B40" s="6">
+        <v>8</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40" s="5"/>
+    </row>
+    <row r="41" spans="1:4" ht="33" customHeight="1">
+      <c r="A41" s="7"/>
+      <c r="B41" s="6">
+        <v>9</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="D41" s="5"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.51181102362204689" footer="0.51181102362204689"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
